--- a/BWI/bestwine_output/bestwine_Indonesia.xlsx
+++ b/BWI/bestwine_output/bestwine_Indonesia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA64"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7300,6 +7300,87 @@
       <c r="Z64" s="2" t="inlineStr"/>
       <c r="AA64" s="2" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PT Maksima Karya Sakti</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Vines Indonesia</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>49840</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Daerah Khusus Ibukota Jakarta, Kota Jakarta Selatan, Kecamatan Kebayoran Baru, Senayan</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Gedung Artha Graha,  Jalan Jenderal Sudirman</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>12190</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://vines-indonesia.com</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>help@vines-indonesia.com</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VINES.Idn/</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vines.indonesia/</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Indonesia.xlsx
+++ b/BWI/bestwine_output/bestwine_Indonesia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7381,6 +7381,192 @@
       <c r="Z65" s="2" t="inlineStr"/>
       <c r="AA65" s="2" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Pt Wonderful Mulia Jaya</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Pt Wonderful Mulia Jaya</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>95587</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Daerah Khusus Ibukota Jakarta, Kota Jakarta Selatan, Kecamatan Kebayoran Baru, Kramat Pela</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>56 Jalan Barito II</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://minuman.com</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>support@minuman.com</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>AHU-32842.AH.01.01.TH 2008</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wonderful-mulia-jaya/</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minuman_com/</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCguJGe9L3onk6rRPW8KlD0g</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Raga Perdana</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>Wines &amp; Spirits Specialist</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raga-perdana-83022398/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>PT Maksima Karya Sakti</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Vines Indonesia</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>49840</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Daerah Khusus Ibukota Jakarta, Kota Jakarta Selatan, Kecamatan Kebayoran Baru, Senayan</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Gedung Artha Graha,  Jalan Jenderal Sudirman</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>12190</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://vines-indonesia.com</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>help@vines-indonesia.com</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VINES.Idn/</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vines.indonesia/</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr"/>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
